--- a/data/cci/cci-platform-programme-mapping.xlsx
+++ b/data/cci/cci-platform-programme-mapping.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsl11288\DOCUME~1\Moba\slash\RemoteFiles\262446_2_1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stfc365-my.sharepoint.com/personal/alison_waterfall_stfc_ac_uk/Documents/Documents/GitHub/cci-vocabularies/data/cci/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BFFCBF6-AA4F-4E3F-8EBA-4AA3B5070369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{8BFFCBF6-AA4F-4E3F-8EBA-4AA3B5070369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC5D5604-3708-46CF-886C-AE21918FEAA6}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{D6294A95-F961-1A4F-9365-26DAE540CA74}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="34515" windowHeight="15285" xr2:uid="{D6294A95-F961-1A4F-9365-26DAE540CA74}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="240">
   <si>
     <t>URI 1</t>
   </si>
@@ -755,6 +755,15 @@
   </si>
   <si>
     <t>plat_noaa_20</t>
+  </si>
+  <si>
+    <t>plat_himawari8</t>
+  </si>
+  <si>
+    <t>plat_himawari9</t>
+  </si>
+  <si>
+    <t>plat_himawari3rd</t>
   </si>
 </sst>
 </file>
@@ -2410,14 +2419,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DF6A92B-36B9-F243-89DF-2828BF9C02CE}">
-  <dimension ref="A1:D174"/>
-  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="14.5"/>
+  <dimension ref="A1:D176"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="25.26953125" customWidth="1"/>
-    <col min="2" max="2" width="31.7265625" customWidth="1"/>
-    <col min="3" max="3" width="22.7265625" customWidth="1"/>
-    <col min="4" max="4" width="34.81640625" customWidth="1"/>
-    <col min="5" max="64" width="13.26953125" customWidth="1"/>
+    <col min="1" max="1" width="25.28515625" customWidth="1"/>
+    <col min="2" max="2" width="31.7109375" customWidth="1"/>
+    <col min="3" max="3" width="22.7109375" customWidth="1"/>
+    <col min="4" max="4" width="34.85546875" customWidth="1"/>
+    <col min="5" max="64" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -3834,7 +3843,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="102" spans="1:4" ht="16.5">
+    <row r="102" spans="1:4" ht="17.25">
       <c r="A102" s="4" t="s">
         <v>130</v>
       </c>
@@ -3848,7 +3857,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="103" spans="1:4" ht="16.5">
+    <row r="103" spans="1:4" ht="17.25">
       <c r="A103" s="4" t="s">
         <v>130</v>
       </c>
@@ -3862,7 +3871,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="104" spans="1:4" ht="16.5">
+    <row r="104" spans="1:4" ht="17.25">
       <c r="A104" s="4" t="s">
         <v>130</v>
       </c>
@@ -3876,7 +3885,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="105" spans="1:4" ht="16.5">
+    <row r="105" spans="1:4" ht="17.25">
       <c r="A105" s="4" t="s">
         <v>130</v>
       </c>
@@ -3890,7 +3899,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="106" spans="1:4" ht="16.5">
+    <row r="106" spans="1:4" ht="17.25">
       <c r="A106" s="4" t="s">
         <v>130</v>
       </c>
@@ -3904,7 +3913,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="107" spans="1:4" ht="16.5">
+    <row r="107" spans="1:4" ht="17.25">
       <c r="A107" s="4" t="s">
         <v>130</v>
       </c>
@@ -3918,7 +3927,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="108" spans="1:4" ht="16.5">
+    <row r="108" spans="1:4" ht="17.25">
       <c r="A108" s="4" t="s">
         <v>130</v>
       </c>
@@ -3932,7 +3941,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="109" spans="1:4" ht="16.5">
+    <row r="109" spans="1:4" ht="17.25">
       <c r="A109" s="4" t="s">
         <v>130</v>
       </c>
@@ -3946,7 +3955,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="110" spans="1:4" ht="16.5">
+    <row r="110" spans="1:4" ht="17.25">
       <c r="A110" s="4" t="s">
         <v>130</v>
       </c>
@@ -3960,7 +3969,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="111" spans="1:4" ht="16.5">
+    <row r="111" spans="1:4" ht="17.25">
       <c r="A111" s="3" t="s">
         <v>140</v>
       </c>
@@ -3974,7 +3983,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="112" spans="1:4" ht="16.5">
+    <row r="112" spans="1:4" ht="17.25">
       <c r="A112" s="3" t="s">
         <v>140</v>
       </c>
@@ -3988,7 +3997,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="113" spans="1:4" ht="16.5">
+    <row r="113" spans="1:4" ht="17.25">
       <c r="A113" s="3" t="s">
         <v>140</v>
       </c>
@@ -4002,7 +4011,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="114" spans="1:4" ht="16.5">
+    <row r="114" spans="1:4" ht="17.25">
       <c r="A114" s="3" t="s">
         <v>140</v>
       </c>
@@ -4016,7 +4025,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="115" spans="1:4" ht="16.5">
+    <row r="115" spans="1:4" ht="17.25">
       <c r="A115" s="3" t="s">
         <v>140</v>
       </c>
@@ -4853,6 +4862,34 @@
         <v>236</v>
       </c>
       <c r="D174" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4">
+      <c r="A175" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B175" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C175" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="D175" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4">
+      <c r="A176" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B176" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C176" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="D176" s="4" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/cci/cci-platform-programme-mapping.xlsx
+++ b/data/cci/cci-platform-programme-mapping.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stfc365-my.sharepoint.com/personal/alison_waterfall_stfc_ac_uk/Documents/Documents/GitHub/cci-vocabularies/data/cci/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{8BFFCBF6-AA4F-4E3F-8EBA-4AA3B5070369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC5D5604-3708-46CF-886C-AE21918FEAA6}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{8BFFCBF6-AA4F-4E3F-8EBA-4AA3B5070369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE7BD992-7F81-4D2E-9CF4-8F72D60E6871}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="34515" windowHeight="15285" xr2:uid="{D6294A95-F961-1A4F-9365-26DAE540CA74}"/>
+    <workbookView xWindow="39105" yWindow="2940" windowWidth="34515" windowHeight="15285" xr2:uid="{D6294A95-F961-1A4F-9365-26DAE540CA74}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -763,7 +763,7 @@
     <t>plat_himawari9</t>
   </si>
   <si>
-    <t>plat_himawari3rd</t>
+    <t>plat_himawari3rd_prog</t>
   </si>
 </sst>
 </file>
